--- a/services/templates/permit_template_default.xlsx
+++ b/services/templates/permit_template_default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mac\Home\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC5656F-21FC-484B-94D3-583B812B7CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54727B47-0267-44DB-9E9A-1C5033452D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="27196" windowHeight="16426" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="27196" windowHeight="16426" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INV" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">INV!$A$1:$G$49</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PL!$A$1:$H$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PL!$A$1:$H$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
   <si>
     <t>WEALDONE LIMITED</t>
   </si>
@@ -58,15 +58,21 @@
     <t xml:space="preserve">DATE: </t>
   </si>
   <si>
-    <t>30-Oct-2026</t>
+    <t>29-Oct-2026</t>
   </si>
   <si>
     <t>Shipping mode:</t>
   </si>
   <si>
+    <t>BY TRUCK</t>
+  </si>
+  <si>
     <t>From:</t>
   </si>
   <si>
+    <t>JIANGSU, CHINA TO PHNOM PENH, CAMBODIA</t>
+  </si>
+  <si>
     <t>Country of origin:</t>
   </si>
   <si>
@@ -166,7 +172,7 @@
     <t>Container /Seal :</t>
   </si>
   <si>
-    <t>FFAU7241358/SITE954434/40HC (PART)</t>
+    <t>1X45 HQ PART OF CFS/CFS</t>
   </si>
   <si>
     <t>INVOICE</t>
@@ -193,9 +199,6 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>CIF SIHANOUK VILLE PORT</t>
-  </si>
-  <si>
     <t>CDC #</t>
   </si>
   <si>
@@ -214,31 +217,27 @@
     <t>DZS</t>
   </si>
   <si>
-    <t>BY TRUCK</t>
-  </si>
-  <si>
-    <t>JIANGSU, CHINA TO PHNOM PENH,CAMBODIA</t>
-  </si>
-  <si>
     <t>PHUM DOMNAK TROYEOUNG, SANGKAT CHOM CHAO II,</t>
   </si>
   <si>
     <t>KHAN POR SEN CHEY PHNOM PENH,</t>
+  </si>
+  <si>
+    <t>DAP PREY VOR BORDER, CAMBODIA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0000000"/>
     <numFmt numFmtId="165" formatCode="[$-409]d/mmm/yy;@"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="#,###\ &quot;P'KGS&quot;"/>
-    <numFmt numFmtId="168" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="#,###\ &quot;PACKAGES&quot;"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="#,###\ &quot;PACKAGES&quot;"/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -450,7 +449,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,8 +462,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -806,6 +811,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -826,7 +842,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="196">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1183,9 +1199,6 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1262,7 +1275,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1280,25 +1293,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="12" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1346,8 +1359,31 @@
     <xf numFmtId="4" fontId="15" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1355,18 +1391,24 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="9" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="2" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1375,29 +1417,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="9" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="2" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -1762,73 +1787,73 @@
     <col min="14" max="14" width="15.53125" style="1" customWidth="1"/>
     <col min="15" max="15" width="16.86328125" style="1" customWidth="1"/>
     <col min="16" max="16" width="17.1328125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.1328125" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.1328125" style="1"/>
+    <col min="17" max="18" width="9.1328125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.8" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="185"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="176"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="176"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="176"/>
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="184"/>
     </row>
     <row r="3" spans="1:13" ht="14.45" customHeight="1">
-      <c r="A3" s="193"/>
-      <c r="B3" s="176"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="176"/>
+      <c r="A3" s="186"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="184"/>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" thickBot="1">
-      <c r="A4" s="194"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="176"/>
+      <c r="A4" s="188"/>
+      <c r="B4" s="184"/>
+      <c r="C4" s="184"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="185"/>
+      <c r="G4" s="184"/>
     </row>
     <row r="5" spans="1:13" ht="13.8" customHeight="1" thickTop="1">
-      <c r="A5" s="136"/>
-      <c r="B5" s="137"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="137"/>
+      <c r="A5" s="135"/>
+      <c r="B5" s="136"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="136"/>
     </row>
     <row r="6" spans="1:13" ht="20.45" customHeight="1">
-      <c r="A6" s="188" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="177"/>
-      <c r="G6" s="176"/>
+      <c r="A6" s="187" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="184"/>
+      <c r="C6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="184"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2"/>
@@ -1847,14 +1872,14 @@
         <v>4</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="189" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="190"/>
+      <c r="D8" s="179" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="180"/>
       <c r="F8" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="160" t="s">
+      <c r="G8" s="159" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1863,7 +1888,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7">
@@ -1871,81 +1896,81 @@
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="10">
         <v>43690</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9" s="141">
+        <v>48</v>
+      </c>
+      <c r="M9" s="140">
         <v>46268</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" s="10">
         <v>43690</v>
       </c>
-      <c r="M10" s="141">
+      <c r="M10" s="140">
         <v>46633</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" s="71"/>
-      <c r="L11" s="141"/>
+      <c r="L11" s="140"/>
     </row>
     <row r="12" spans="1:13" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="135" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B12" s="134" t="s">
+        <v>14</v>
       </c>
       <c r="F12" s="71"/>
     </row>
     <row r="13" spans="1:13" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B13" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="71"/>
     </row>
     <row r="14" spans="1:13" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F14" s="71"/>
     </row>
     <row r="15" spans="1:13" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F15" s="71"/>
     </row>
     <row r="16" spans="1:13" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F16" s="71"/>
     </row>
     <row r="17" spans="1:16" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B17" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17" s="71"/>
     </row>
@@ -1957,21 +1982,21 @@
     </row>
     <row r="20" spans="1:16" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1" thickBot="1">
       <c r="A20" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="178" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="180"/>
-      <c r="D20" s="178" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="180"/>
+        <v>50</v>
+      </c>
+      <c r="B20" s="181" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="182"/>
+      <c r="D20" s="181" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="182"/>
       <c r="F20" s="72" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1">
@@ -1980,387 +2005,387 @@
       <c r="D21" s="15"/>
       <c r="E21" s="16"/>
       <c r="F21" s="75" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G21" s="17"/>
       <c r="H21" s="25"/>
     </row>
     <row r="22" spans="1:16" s="35" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="27"/>
       <c r="C22" s="28"/>
       <c r="D22" s="78"/>
       <c r="E22" s="29"/>
       <c r="F22" s="79" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H22" s="34"/>
     </row>
     <row r="23" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A23" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="145" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="146"/>
+        <v>55</v>
+      </c>
+      <c r="B23" s="144" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="145"/>
       <c r="D23" s="78"/>
       <c r="E23" s="29"/>
       <c r="F23" s="84"/>
       <c r="G23" s="30"/>
       <c r="H23" s="34"/>
       <c r="J23" s="35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K23" s="35" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L23" s="35" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M23" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="N23" s="148" t="s">
-        <v>56</v>
+        <v>27</v>
+      </c>
+      <c r="N23" s="147" t="s">
+        <v>57</v>
       </c>
       <c r="O23" s="58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A24" s="161">
+      <c r="A24" s="160">
         <v>4</v>
       </c>
-      <c r="B24" s="162" t="s">
-        <v>26</v>
+      <c r="B24" s="161" t="s">
+        <v>28</v>
       </c>
       <c r="C24" s="38"/>
-      <c r="D24" s="163">
+      <c r="D24" s="162">
         <v>6406</v>
       </c>
-      <c r="E24" s="164" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="165">
+      <c r="E24" s="163" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="164">
         <v>4.5</v>
       </c>
-      <c r="G24" s="166">
+      <c r="G24" s="165">
         <f t="shared" ref="G24:G33" si="0">D24*F24</f>
         <v>28827</v>
       </c>
       <c r="H24" s="49"/>
       <c r="I24" s="49"/>
-      <c r="J24" s="123"/>
-      <c r="K24" s="152"/>
-      <c r="L24" s="142"/>
-      <c r="M24" s="142"/>
-      <c r="N24" s="143"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="151"/>
+      <c r="L24" s="141"/>
+      <c r="M24" s="141"/>
+      <c r="N24" s="142"/>
     </row>
     <row r="25" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A25" s="161">
+      <c r="A25" s="160">
         <v>13</v>
       </c>
-      <c r="B25" s="167" t="s">
-        <v>28</v>
+      <c r="B25" s="166" t="s">
+        <v>30</v>
       </c>
       <c r="C25" s="38"/>
-      <c r="D25" s="163">
+      <c r="D25" s="162">
         <v>5905</v>
       </c>
-      <c r="E25" s="164" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="165">
+      <c r="E25" s="163" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="164">
         <v>0.04</v>
       </c>
-      <c r="G25" s="166">
+      <c r="G25" s="165">
         <f t="shared" si="0"/>
         <v>236.20000000000002</v>
       </c>
       <c r="H25" s="49"/>
       <c r="I25" s="49"/>
-      <c r="J25" s="123"/>
-      <c r="K25" s="152"/>
-      <c r="L25" s="142"/>
-      <c r="M25" s="142"/>
-      <c r="N25" s="143"/>
+      <c r="J25" s="122"/>
+      <c r="K25" s="151"/>
+      <c r="L25" s="141"/>
+      <c r="M25" s="141"/>
+      <c r="N25" s="142"/>
     </row>
     <row r="26" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A26" s="161">
+      <c r="A26" s="160">
         <v>14</v>
       </c>
-      <c r="B26" s="167" t="s">
-        <v>30</v>
+      <c r="B26" s="166" t="s">
+        <v>32</v>
       </c>
       <c r="C26" s="41"/>
-      <c r="D26" s="163">
+      <c r="D26" s="162">
         <v>2113</v>
       </c>
-      <c r="E26" s="164" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="165">
+      <c r="E26" s="163" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="164">
         <v>0.2</v>
       </c>
-      <c r="G26" s="166">
+      <c r="G26" s="165">
         <f t="shared" si="0"/>
         <v>422.6</v>
       </c>
       <c r="H26" s="49"/>
       <c r="I26" s="49"/>
-      <c r="J26" s="149"/>
-      <c r="K26" s="153"/>
-      <c r="L26" s="149"/>
-      <c r="M26" s="149"/>
-      <c r="N26" s="147"/>
-      <c r="O26" s="143"/>
-      <c r="P26" s="143"/>
+      <c r="J26" s="148"/>
+      <c r="K26" s="152"/>
+      <c r="L26" s="148"/>
+      <c r="M26" s="148"/>
+      <c r="N26" s="146"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="142"/>
     </row>
     <row r="27" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A27" s="161">
+      <c r="A27" s="160">
         <v>17</v>
       </c>
-      <c r="B27" s="167" t="s">
-        <v>32</v>
+      <c r="B27" s="166" t="s">
+        <v>34</v>
       </c>
       <c r="C27" s="38"/>
-      <c r="D27" s="163">
+      <c r="D27" s="162">
         <v>2113</v>
       </c>
-      <c r="E27" s="164" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="165">
+      <c r="E27" s="163" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="164">
         <v>0.15</v>
       </c>
-      <c r="G27" s="166">
+      <c r="G27" s="165">
         <f t="shared" si="0"/>
         <v>316.95</v>
       </c>
       <c r="H27" s="49"/>
       <c r="I27" s="49"/>
-      <c r="J27" s="149"/>
-      <c r="K27" s="153"/>
-      <c r="L27" s="149"/>
-      <c r="M27" s="149"/>
-      <c r="N27" s="154"/>
-      <c r="O27" s="143"/>
+      <c r="J27" s="148"/>
+      <c r="K27" s="152"/>
+      <c r="L27" s="148"/>
+      <c r="M27" s="148"/>
+      <c r="N27" s="153"/>
+      <c r="O27" s="142"/>
     </row>
     <row r="28" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A28" s="161">
+      <c r="A28" s="160">
         <v>26</v>
       </c>
-      <c r="B28" s="168" t="s">
+      <c r="B28" s="167" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="38"/>
+      <c r="D28" s="162">
+        <v>2120</v>
+      </c>
+      <c r="E28" s="163" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="38"/>
-      <c r="D28" s="163">
-        <v>2120</v>
-      </c>
-      <c r="E28" s="164" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="165">
+      <c r="F28" s="164">
         <v>1</v>
       </c>
-      <c r="G28" s="166">
+      <c r="G28" s="165">
         <f t="shared" si="0"/>
         <v>2120</v>
       </c>
       <c r="H28" s="49"/>
       <c r="I28" s="49"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="156"/>
-      <c r="L28" s="155"/>
-      <c r="M28" s="155"/>
-      <c r="N28" s="157"/>
-      <c r="O28" s="154"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="155"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="156"/>
+      <c r="O28" s="153"/>
     </row>
     <row r="29" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A29" s="161">
+      <c r="A29" s="160">
         <v>28</v>
       </c>
-      <c r="B29" s="162" t="s">
-        <v>34</v>
+      <c r="B29" s="161" t="s">
+        <v>36</v>
       </c>
       <c r="C29" s="38"/>
-      <c r="D29" s="163">
+      <c r="D29" s="162">
         <v>407</v>
       </c>
-      <c r="E29" s="164" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="165">
-        <v>8.6570999999999998</v>
-      </c>
-      <c r="G29" s="166">
+      <c r="E29" s="163" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="164">
+        <v>3</v>
+      </c>
+      <c r="G29" s="165">
         <f t="shared" si="0"/>
-        <v>3523.4396999999999</v>
+        <v>1221</v>
       </c>
       <c r="H29" s="49"/>
       <c r="I29" s="49"/>
-      <c r="J29" s="155"/>
-      <c r="K29" s="156"/>
-      <c r="L29" s="155"/>
-      <c r="M29" s="155"/>
-      <c r="N29" s="156"/>
-      <c r="O29" s="156"/>
-      <c r="P29" s="158"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="155"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
+      <c r="N29" s="155"/>
+      <c r="O29" s="155"/>
+      <c r="P29" s="157"/>
     </row>
     <row r="30" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A30" s="161">
+      <c r="A30" s="160">
         <v>29</v>
       </c>
-      <c r="B30" s="162" t="s">
-        <v>36</v>
+      <c r="B30" s="161" t="s">
+        <v>38</v>
       </c>
       <c r="C30" s="38"/>
-      <c r="D30" s="163">
+      <c r="D30" s="162">
         <v>284</v>
       </c>
-      <c r="E30" s="164" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="165">
+      <c r="E30" s="163" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="164">
         <v>3</v>
       </c>
-      <c r="G30" s="166">
+      <c r="G30" s="165">
         <f t="shared" si="0"/>
         <v>852</v>
       </c>
       <c r="H30" s="49"/>
       <c r="I30" s="49"/>
-      <c r="J30" s="149"/>
-      <c r="K30" s="153"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="149"/>
-      <c r="N30" s="153"/>
-      <c r="O30" s="154"/>
+      <c r="J30" s="148"/>
+      <c r="K30" s="152"/>
+      <c r="L30" s="148"/>
+      <c r="M30" s="148"/>
+      <c r="N30" s="152"/>
+      <c r="O30" s="153"/>
     </row>
     <row r="31" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A31" s="161">
+      <c r="A31" s="160">
         <v>31</v>
       </c>
-      <c r="B31" s="162" t="s">
+      <c r="B31" s="161" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="38"/>
+      <c r="D31" s="162">
+        <v>1201</v>
+      </c>
+      <c r="E31" s="163" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="38"/>
-      <c r="D31" s="163">
-        <v>1201</v>
-      </c>
-      <c r="E31" s="164" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31" s="165">
+      <c r="F31" s="164">
         <v>1.2</v>
       </c>
-      <c r="G31" s="166">
+      <c r="G31" s="165">
         <f t="shared" si="0"/>
         <v>1441.2</v>
       </c>
-      <c r="H31" s="125"/>
+      <c r="H31" s="124"/>
       <c r="I31" s="49"/>
-      <c r="J31" s="149"/>
-      <c r="K31" s="150"/>
-      <c r="L31" s="151"/>
-      <c r="M31" s="151"/>
-      <c r="N31" s="147"/>
-      <c r="O31" s="143"/>
+      <c r="J31" s="148"/>
+      <c r="K31" s="149"/>
+      <c r="L31" s="150"/>
+      <c r="M31" s="150"/>
+      <c r="N31" s="146"/>
+      <c r="O31" s="142"/>
     </row>
     <row r="32" spans="1:16" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A32" s="161">
+      <c r="A32" s="160">
         <v>61</v>
       </c>
-      <c r="B32" s="162" t="s">
-        <v>38</v>
+      <c r="B32" s="161" t="s">
+        <v>40</v>
       </c>
       <c r="C32" s="38"/>
-      <c r="D32" s="163">
+      <c r="D32" s="162">
         <v>518</v>
       </c>
-      <c r="E32" s="164" t="s">
-        <v>35</v>
-      </c>
-      <c r="F32" s="165">
+      <c r="E32" s="163" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="164">
         <v>1</v>
       </c>
-      <c r="G32" s="166">
+      <c r="G32" s="165">
         <f t="shared" si="0"/>
         <v>518</v>
       </c>
-      <c r="H32" s="125"/>
+      <c r="H32" s="124"/>
       <c r="I32" s="49"/>
-      <c r="J32" s="149">
+      <c r="J32" s="148">
         <f t="shared" ref="J32:O32" si="1">SUM(J24:J30)</f>
         <v>0</v>
       </c>
-      <c r="K32" s="153">
+      <c r="K32" s="152">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L32" s="149">
+      <c r="L32" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M32" s="149">
+      <c r="M32" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N32" s="153">
+      <c r="N32" s="152">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O32" s="149">
+      <c r="O32" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A33" s="161">
+      <c r="A33" s="160">
         <v>86</v>
       </c>
-      <c r="B33" s="162" t="s">
-        <v>39</v>
+      <c r="B33" s="161" t="s">
+        <v>41</v>
       </c>
       <c r="C33" s="38"/>
-      <c r="D33" s="163">
+      <c r="D33" s="162">
         <v>141600</v>
       </c>
-      <c r="E33" s="164" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="165">
+      <c r="E33" s="163" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="164">
         <v>0.01</v>
       </c>
-      <c r="G33" s="166">
+      <c r="G33" s="165">
         <f t="shared" si="0"/>
         <v>1416</v>
       </c>
-      <c r="H33" s="125"/>
+      <c r="H33" s="124"/>
       <c r="I33" s="49"/>
-      <c r="J33" s="149"/>
-      <c r="K33" s="150"/>
-      <c r="L33" s="151"/>
-      <c r="M33" s="151"/>
-      <c r="N33" s="154"/>
-      <c r="O33" s="143"/>
+      <c r="J33" s="148"/>
+      <c r="K33" s="149"/>
+      <c r="L33" s="150"/>
+      <c r="M33" s="150"/>
+      <c r="N33" s="153"/>
+      <c r="O33" s="142"/>
     </row>
     <row r="34" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A34" s="39"/>
       <c r="C34" s="38"/>
       <c r="D34" s="40"/>
       <c r="E34" s="41"/>
-      <c r="F34" s="123"/>
-      <c r="G34" s="124"/>
-      <c r="H34" s="125"/>
+      <c r="F34" s="122"/>
+      <c r="G34" s="123"/>
+      <c r="H34" s="124"/>
       <c r="I34" s="49"/>
-      <c r="J34" s="123"/>
+      <c r="J34" s="122"/>
       <c r="K34" s="49"/>
     </row>
     <row r="35" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1">
@@ -2368,11 +2393,11 @@
       <c r="C35" s="38"/>
       <c r="D35" s="40"/>
       <c r="E35" s="41"/>
-      <c r="F35" s="123"/>
-      <c r="G35" s="124"/>
-      <c r="H35" s="125"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="123"/>
+      <c r="H35" s="124"/>
       <c r="I35" s="49"/>
-      <c r="J35" s="123"/>
+      <c r="J35" s="122"/>
       <c r="K35" s="49"/>
     </row>
     <row r="36" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1">
@@ -2380,43 +2405,43 @@
       <c r="C36" s="38"/>
       <c r="D36" s="40"/>
       <c r="E36" s="41"/>
-      <c r="F36" s="123"/>
-      <c r="G36" s="124"/>
+      <c r="F36" s="122"/>
+      <c r="G36" s="123"/>
       <c r="H36" s="49"/>
       <c r="I36" s="49"/>
-      <c r="J36" s="149"/>
-      <c r="K36" s="153"/>
-      <c r="L36" s="149"/>
-      <c r="M36" s="149"/>
-      <c r="N36" s="154"/>
-      <c r="O36" s="154"/>
+      <c r="J36" s="148"/>
+      <c r="K36" s="152"/>
+      <c r="L36" s="148"/>
+      <c r="M36" s="148"/>
+      <c r="N36" s="153"/>
+      <c r="O36" s="153"/>
     </row>
     <row r="37" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A37" s="39"/>
       <c r="C37" s="38"/>
       <c r="D37" s="40"/>
       <c r="E37" s="41"/>
-      <c r="F37" s="123"/>
-      <c r="G37" s="124"/>
+      <c r="F37" s="122"/>
+      <c r="G37" s="123"/>
       <c r="H37" s="49"/>
       <c r="I37" s="49"/>
-      <c r="J37" s="155"/>
-      <c r="K37" s="156"/>
-      <c r="L37" s="155"/>
-      <c r="M37" s="155"/>
-      <c r="N37" s="157"/>
-      <c r="O37" s="154"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="155"/>
+      <c r="L37" s="154"/>
+      <c r="M37" s="154"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="153"/>
     </row>
     <row r="38" spans="1:15" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A38" s="39"/>
       <c r="C38" s="38"/>
       <c r="D38" s="40"/>
       <c r="E38" s="41"/>
-      <c r="F38" s="123"/>
-      <c r="G38" s="124"/>
+      <c r="F38" s="122"/>
+      <c r="G38" s="123"/>
       <c r="H38" s="49"/>
       <c r="I38" s="49"/>
-      <c r="J38" s="123"/>
+      <c r="J38" s="122"/>
       <c r="K38" s="49"/>
     </row>
     <row r="39" spans="1:15" s="35" customFormat="1" ht="16.8" customHeight="1">
@@ -2439,15 +2464,15 @@
       <c r="D40" s="89"/>
       <c r="E40" s="90"/>
       <c r="F40" s="91"/>
-      <c r="G40" s="169">
+      <c r="G40" s="168">
         <f>SUM(G24:G33)</f>
-        <v>39673.3897</v>
+        <v>37370.949999999997</v>
       </c>
       <c r="H40" s="34"/>
       <c r="I40" s="34"/>
     </row>
     <row r="41" spans="1:15" s="35" customFormat="1" ht="17.45" customHeight="1" thickTop="1">
-      <c r="A41" s="52"/>
+      <c r="A41" s="197"/>
       <c r="B41" s="53"/>
       <c r="C41" s="54"/>
       <c r="D41" s="94"/>
@@ -2474,11 +2499,11 @@
       <c r="B43" s="55"/>
       <c r="C43" s="56"/>
       <c r="D43" s="60"/>
-      <c r="E43" s="191" t="s">
+      <c r="E43" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="F43" s="182"/>
-      <c r="G43" s="183"/>
+      <c r="F43" s="177"/>
+      <c r="G43" s="178"/>
     </row>
     <row r="44" spans="1:15" s="35" customFormat="1" ht="16.8" customHeight="1">
       <c r="A44" s="52"/>
@@ -2490,7 +2515,7 @@
       <c r="G44" s="62"/>
     </row>
     <row r="45" spans="1:15" ht="16.8" customHeight="1">
-      <c r="A45" s="55"/>
+      <c r="A45" s="198"/>
       <c r="B45" s="55"/>
       <c r="C45" s="55"/>
       <c r="D45" s="55"/>
@@ -2499,7 +2524,7 @@
       <c r="G45" s="66"/>
     </row>
     <row r="46" spans="1:15" ht="16.8" customHeight="1">
-      <c r="A46" s="55"/>
+      <c r="A46" s="198"/>
       <c r="B46" s="55"/>
       <c r="C46" s="55"/>
       <c r="D46" s="55"/>
@@ -2508,7 +2533,7 @@
       <c r="G46" s="66"/>
     </row>
     <row r="47" spans="1:15" ht="16.8" customHeight="1">
-      <c r="A47" s="55"/>
+      <c r="A47" s="198"/>
       <c r="B47" s="55"/>
       <c r="C47" s="55"/>
       <c r="D47" s="55"/>
@@ -2517,13 +2542,13 @@
       <c r="G47" s="66"/>
     </row>
     <row r="48" spans="1:15" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A48" s="126"/>
-      <c r="B48" s="127"/>
-      <c r="C48" s="127"/>
-      <c r="D48" s="128"/>
-      <c r="E48" s="128"/>
-      <c r="F48" s="129"/>
-      <c r="G48" s="130"/>
+      <c r="A48" s="125"/>
+      <c r="B48" s="126"/>
+      <c r="C48" s="126"/>
+      <c r="D48" s="127"/>
+      <c r="E48" s="127"/>
+      <c r="F48" s="128"/>
+      <c r="G48" s="129"/>
     </row>
     <row r="49" spans="4:7" ht="13.8" customHeight="1" thickTop="1">
       <c r="D49" s="65"/>
@@ -2557,13 +2582,13 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="E43:G43"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="D20:E20"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
@@ -2585,7 +2610,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:AJ52"/>
+  <dimension ref="A1:AJ53"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="13.15"/>
   <cols>
     <col min="1" max="1" width="19.53125" style="1" customWidth="1"/>
@@ -2598,75 +2623,75 @@
     <col min="8" max="8" width="15.46484375" style="69" customWidth="1"/>
     <col min="9" max="9" width="10.6640625" style="69" customWidth="1"/>
     <col min="10" max="10" width="10.86328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="9.1328125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="11" max="14" width="9.1328125" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.8" customHeight="1">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="192" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
-      <c r="G1" s="176"/>
-      <c r="H1" s="177"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="185"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="175" t="s">
+      <c r="A2" s="191" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="176"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="176"/>
-      <c r="F2" s="176"/>
-      <c r="G2" s="176"/>
-      <c r="H2" s="177"/>
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="184"/>
+      <c r="G2" s="184"/>
+      <c r="H2" s="185"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="175"/>
-      <c r="B3" s="176"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="177"/>
+      <c r="A3" s="191"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="185"/>
     </row>
     <row r="4" spans="1:9" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A4" s="175"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="176"/>
-      <c r="H4" s="177"/>
+      <c r="A4" s="191"/>
+      <c r="B4" s="184"/>
+      <c r="C4" s="184"/>
+      <c r="D4" s="184"/>
+      <c r="E4" s="184"/>
+      <c r="F4" s="184"/>
+      <c r="G4" s="184"/>
+      <c r="H4" s="185"/>
     </row>
     <row r="5" spans="1:9" ht="21" customHeight="1" thickTop="1">
-      <c r="A5" s="137"/>
-      <c r="B5" s="137"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="139"/>
+      <c r="A5" s="136"/>
+      <c r="B5" s="136"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="138"/>
     </row>
     <row r="6" spans="1:9" ht="20.45" customHeight="1">
-      <c r="A6" s="188" t="s">
+      <c r="A6" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
-      <c r="H6" s="177"/>
+      <c r="B6" s="184"/>
+      <c r="C6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
+      <c r="F6" s="184"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="185"/>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -2678,7 +2703,7 @@
       <c r="G8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="120" t="s">
+      <c r="H8" s="159" t="s">
         <v>6</v>
       </c>
       <c r="I8" s="71"/>
@@ -2688,262 +2713,236 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="H9" s="71"/>
       <c r="I9" s="71"/>
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="H10" s="71"/>
       <c r="I10" s="71"/>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H11" s="71"/>
       <c r="I11" s="71"/>
     </row>
     <row r="12" spans="1:9" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="134" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B12" s="133" t="s">
+        <v>14</v>
       </c>
       <c r="H12" s="71"/>
       <c r="I12" s="71"/>
     </row>
     <row r="13" spans="1:9" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B13" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H13" s="71"/>
       <c r="I13" s="71"/>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H14" s="71"/>
       <c r="I14" s="71"/>
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" ht="13.8" customHeight="1">
-      <c r="B15" s="6" t="s">
-        <v>14</v>
+      <c r="B15" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H15" s="71"/>
       <c r="I15" s="71"/>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B16" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="71"/>
       <c r="I16" s="71"/>
     </row>
     <row r="17" spans="1:19" s="3" customFormat="1" ht="13.8" customHeight="1">
-      <c r="B17" s="6"/>
+      <c r="B17" s="6" t="s">
+        <v>17</v>
+      </c>
       <c r="H17" s="71"/>
       <c r="I17" s="71"/>
     </row>
-    <row r="18" spans="1:19" s="3" customFormat="1" ht="14.45" customHeight="1" thickBot="1">
+    <row r="18" spans="1:19" s="3" customFormat="1" ht="13.8" customHeight="1">
       <c r="B18" s="6"/>
       <c r="H18" s="71"/>
       <c r="I18" s="71"/>
     </row>
-    <row r="19" spans="1:19" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A19" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="178" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="179"/>
-      <c r="D19" s="180"/>
-      <c r="E19" s="178" t="s">
+    <row r="19" spans="1:19" s="3" customFormat="1" ht="14.45" customHeight="1" thickBot="1">
+      <c r="B19" s="6"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+    </row>
+    <row r="20" spans="1:19" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="180"/>
-      <c r="G19" s="13" t="s">
+      <c r="B20" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="73" t="s">
+      <c r="C20" s="196"/>
+      <c r="D20" s="182"/>
+      <c r="E20" s="181" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="71"/>
-    </row>
-    <row r="20" spans="1:19" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="25"/>
-    </row>
-    <row r="21" spans="1:19" s="35" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A21" s="26"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="79" t="s">
+      <c r="F20" s="182"/>
+      <c r="G20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="82" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="83"/>
-      <c r="J21" s="34"/>
-    </row>
-    <row r="22" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
+      <c r="H20" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="71"/>
+    </row>
+    <row r="21" spans="1:19" s="3" customFormat="1" ht="15" customHeight="1" thickTop="1">
+      <c r="A21" s="18"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="76"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="25"/>
+    </row>
+    <row r="22" spans="1:19" s="35" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="26"/>
-      <c r="B22" s="37" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="35" t="s">
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="K22" s="35" t="s">
+      <c r="H22" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="83"/>
+      <c r="J22" s="34"/>
+    </row>
+    <row r="23" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
+      <c r="A23" s="26"/>
+      <c r="B23" s="37" t="s">
         <v>24</v>
-      </c>
-      <c r="L22" s="35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A23" s="170">
-        <v>284</v>
-      </c>
-      <c r="B23" s="167" t="s">
-        <v>26</v>
       </c>
       <c r="C23" s="38"/>
       <c r="D23" s="38"/>
-      <c r="E23" s="163">
-        <v>6406</v>
-      </c>
-      <c r="F23" s="171" t="s">
+      <c r="E23" s="45"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="172">
-        <v>6406</v>
-      </c>
-      <c r="H23" s="166">
-        <v>6690</v>
-      </c>
-      <c r="I23" s="48"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="142"/>
     </row>
     <row r="24" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A24" s="170">
-        <v>1</v>
-      </c>
-      <c r="B24" s="167" t="s">
+      <c r="A24" s="169">
+        <v>284</v>
+      </c>
+      <c r="B24" s="166" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="38"/>
       <c r="D24" s="38"/>
-      <c r="E24" s="163">
-        <v>5905</v>
-      </c>
-      <c r="F24" s="171" t="s">
+      <c r="E24" s="162">
+        <v>6406</v>
+      </c>
+      <c r="F24" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="172">
-        <v>13</v>
-      </c>
-      <c r="H24" s="166">
-        <v>14</v>
+      <c r="G24" s="171">
+        <v>6406</v>
+      </c>
+      <c r="H24" s="165">
+        <v>6690</v>
       </c>
       <c r="I24" s="48"/>
       <c r="J24" s="49"/>
-      <c r="K24" s="123"/>
-      <c r="L24" s="123"/>
-      <c r="M24" s="142"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="141"/>
     </row>
     <row r="25" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A25" s="170">
-        <v>3</v>
-      </c>
-      <c r="B25" s="167" t="s">
+      <c r="A25" s="169">
+        <v>1</v>
+      </c>
+      <c r="B25" s="166" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="38"/>
       <c r="D25" s="38"/>
-      <c r="E25" s="163">
-        <v>2113</v>
-      </c>
-      <c r="F25" s="171" t="s">
+      <c r="E25" s="162">
+        <v>5905</v>
+      </c>
+      <c r="F25" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="G25" s="172">
-        <v>28.5</v>
-      </c>
-      <c r="H25" s="166">
-        <v>33</v>
+      <c r="G25" s="171">
+        <v>13</v>
+      </c>
+      <c r="H25" s="165">
+        <v>14</v>
       </c>
       <c r="I25" s="48"/>
       <c r="J25" s="49"/>
-      <c r="K25" s="123"/>
-      <c r="L25" s="123"/>
-      <c r="M25" s="49"/>
-      <c r="N25" s="49"/>
-      <c r="O25" s="49"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="49"/>
-      <c r="R25" s="49"/>
-      <c r="S25" s="49"/>
+      <c r="K25" s="122"/>
+      <c r="L25" s="122"/>
+      <c r="M25" s="141"/>
     </row>
     <row r="26" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A26" s="170">
-        <v>1</v>
-      </c>
-      <c r="B26" s="167" t="s">
+      <c r="A26" s="169">
+        <v>3</v>
+      </c>
+      <c r="B26" s="166" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="38"/>
       <c r="D26" s="38"/>
-      <c r="E26" s="163">
+      <c r="E26" s="162">
         <v>2113</v>
       </c>
-      <c r="F26" s="171" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="172">
-        <v>20.5</v>
-      </c>
-      <c r="H26" s="166">
-        <v>22</v>
+      <c r="F26" s="170" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="171">
+        <v>28.5</v>
+      </c>
+      <c r="H26" s="165">
+        <v>33</v>
       </c>
       <c r="I26" s="48"/>
       <c r="J26" s="49"/>
-      <c r="K26" s="123"/>
-      <c r="L26" s="123"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="122"/>
       <c r="M26" s="49"/>
       <c r="N26" s="49"/>
       <c r="O26" s="49"/>
@@ -2953,30 +2952,30 @@
       <c r="S26" s="49"/>
     </row>
     <row r="27" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A27" s="170">
-        <v>38</v>
-      </c>
-      <c r="B27" s="167" t="s">
-        <v>33</v>
+      <c r="A27" s="169">
+        <v>1</v>
+      </c>
+      <c r="B27" s="166" t="s">
+        <v>34</v>
       </c>
       <c r="C27" s="38"/>
       <c r="D27" s="38"/>
-      <c r="E27" s="163">
-        <v>2120</v>
-      </c>
-      <c r="F27" s="171" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="172">
-        <v>913</v>
-      </c>
-      <c r="H27" s="166">
-        <v>970</v>
+      <c r="E27" s="162">
+        <v>2113</v>
+      </c>
+      <c r="F27" s="170" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="171">
+        <v>20.5</v>
+      </c>
+      <c r="H27" s="165">
+        <v>22</v>
       </c>
       <c r="I27" s="48"/>
       <c r="J27" s="49"/>
-      <c r="K27" s="123"/>
-      <c r="L27" s="123"/>
+      <c r="K27" s="122"/>
+      <c r="L27" s="122"/>
       <c r="M27" s="49"/>
       <c r="N27" s="49"/>
       <c r="O27" s="49"/>
@@ -2986,30 +2985,30 @@
       <c r="S27" s="49"/>
     </row>
     <row r="28" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A28" s="170">
-        <v>36</v>
-      </c>
-      <c r="B28" s="167" t="s">
-        <v>34</v>
+      <c r="A28" s="169">
+        <v>38</v>
+      </c>
+      <c r="B28" s="166" t="s">
+        <v>35</v>
       </c>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
-      <c r="E28" s="163">
-        <v>407</v>
-      </c>
-      <c r="F28" s="171" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" s="172">
-        <v>1118</v>
-      </c>
-      <c r="H28" s="166">
-        <v>1154</v>
+      <c r="E28" s="162">
+        <v>2120</v>
+      </c>
+      <c r="F28" s="170" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="171">
+        <v>913</v>
+      </c>
+      <c r="H28" s="165">
+        <v>970</v>
       </c>
       <c r="I28" s="48"/>
       <c r="J28" s="49"/>
-      <c r="K28" s="123"/>
-      <c r="L28" s="123"/>
+      <c r="K28" s="122"/>
+      <c r="L28" s="122"/>
       <c r="M28" s="49"/>
       <c r="N28" s="49"/>
       <c r="O28" s="49"/>
@@ -3019,30 +3018,30 @@
       <c r="S28" s="49"/>
     </row>
     <row r="29" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A29" s="170">
-        <v>12</v>
-      </c>
-      <c r="B29" s="167" t="s">
+      <c r="A29" s="169">
+        <v>36</v>
+      </c>
+      <c r="B29" s="166" t="s">
         <v>36</v>
       </c>
       <c r="C29" s="38"/>
       <c r="D29" s="38"/>
-      <c r="E29" s="163">
-        <v>284</v>
-      </c>
-      <c r="F29" s="171" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="172">
-        <v>284</v>
-      </c>
-      <c r="H29" s="166">
-        <v>296</v>
+      <c r="E29" s="162">
+        <v>407</v>
+      </c>
+      <c r="F29" s="170" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="171">
+        <v>1118</v>
+      </c>
+      <c r="H29" s="165">
+        <v>1154</v>
       </c>
       <c r="I29" s="48"/>
       <c r="J29" s="49"/>
-      <c r="K29" s="123"/>
-      <c r="L29" s="123"/>
+      <c r="K29" s="122"/>
+      <c r="L29" s="122"/>
       <c r="M29" s="49"/>
       <c r="N29" s="49"/>
       <c r="O29" s="49"/>
@@ -3052,30 +3051,30 @@
       <c r="S29" s="49"/>
     </row>
     <row r="30" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A30" s="170">
-        <v>2</v>
-      </c>
-      <c r="B30" s="167" t="s">
-        <v>37</v>
+      <c r="A30" s="169">
+        <v>12</v>
+      </c>
+      <c r="B30" s="166" t="s">
+        <v>38</v>
       </c>
       <c r="C30" s="38"/>
       <c r="D30" s="38"/>
-      <c r="E30" s="163">
-        <v>1201</v>
-      </c>
-      <c r="F30" s="171" t="s">
-        <v>35</v>
-      </c>
-      <c r="G30" s="172">
-        <v>37</v>
-      </c>
-      <c r="H30" s="166">
-        <v>40</v>
+      <c r="E30" s="162">
+        <v>284</v>
+      </c>
+      <c r="F30" s="170" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="171">
+        <v>284</v>
+      </c>
+      <c r="H30" s="165">
+        <v>296</v>
       </c>
       <c r="I30" s="48"/>
       <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="49"/>
+      <c r="K30" s="122"/>
+      <c r="L30" s="122"/>
       <c r="M30" s="49"/>
       <c r="N30" s="49"/>
       <c r="O30" s="49"/>
@@ -3085,25 +3084,25 @@
       <c r="S30" s="49"/>
     </row>
     <row r="31" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A31" s="170">
-        <v>4</v>
-      </c>
-      <c r="B31" s="167" t="s">
-        <v>38</v>
+      <c r="A31" s="169">
+        <v>2</v>
+      </c>
+      <c r="B31" s="166" t="s">
+        <v>39</v>
       </c>
       <c r="C31" s="38"/>
       <c r="D31" s="38"/>
-      <c r="E31" s="163">
-        <v>518</v>
-      </c>
-      <c r="F31" s="171" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" s="172">
-        <v>51</v>
-      </c>
-      <c r="H31" s="166">
-        <v>57</v>
+      <c r="E31" s="162">
+        <v>1201</v>
+      </c>
+      <c r="F31" s="170" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="171">
+        <v>37</v>
+      </c>
+      <c r="H31" s="165">
+        <v>40</v>
       </c>
       <c r="I31" s="48"/>
       <c r="J31" s="49"/>
@@ -3118,25 +3117,25 @@
       <c r="S31" s="49"/>
     </row>
     <row r="32" spans="1:19" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A32" s="170">
-        <v>9</v>
-      </c>
-      <c r="B32" s="167" t="s">
-        <v>39</v>
+      <c r="A32" s="169">
+        <v>4</v>
+      </c>
+      <c r="B32" s="166" t="s">
+        <v>40</v>
       </c>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
-      <c r="E32" s="163">
-        <v>141600</v>
-      </c>
-      <c r="F32" s="171" t="s">
-        <v>40</v>
-      </c>
-      <c r="G32" s="172">
-        <v>239.5</v>
-      </c>
-      <c r="H32" s="166">
-        <v>253</v>
+      <c r="E32" s="162">
+        <v>518</v>
+      </c>
+      <c r="F32" s="170" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="171">
+        <v>51</v>
+      </c>
+      <c r="H32" s="165">
+        <v>57</v>
       </c>
       <c r="I32" s="48"/>
       <c r="J32" s="49"/>
@@ -3151,14 +3150,26 @@
       <c r="S32" s="49"/>
     </row>
     <row r="33" spans="1:36" s="35" customFormat="1" ht="18" customHeight="1">
-      <c r="A33" s="44"/>
-      <c r="B33" s="121"/>
+      <c r="A33" s="169">
+        <v>9</v>
+      </c>
+      <c r="B33" s="166" t="s">
+        <v>41</v>
+      </c>
       <c r="C33" s="38"/>
       <c r="D33" s="38"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="47"/>
+      <c r="E33" s="162">
+        <v>141600</v>
+      </c>
+      <c r="F33" s="170" t="s">
+        <v>42</v>
+      </c>
+      <c r="G33" s="171">
+        <v>239.5</v>
+      </c>
+      <c r="H33" s="165">
+        <v>253</v>
+      </c>
       <c r="I33" s="48"/>
       <c r="J33" s="49"/>
       <c r="K33" s="49"/>
@@ -3173,7 +3184,7 @@
     </row>
     <row r="34" spans="1:36" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A34" s="44"/>
-      <c r="B34" s="121"/>
+      <c r="B34" s="120"/>
       <c r="C34" s="38"/>
       <c r="D34" s="38"/>
       <c r="E34" s="45"/>
@@ -3194,7 +3205,7 @@
     </row>
     <row r="35" spans="1:36" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A35" s="44"/>
-      <c r="B35" s="121"/>
+      <c r="B35" s="120"/>
       <c r="C35" s="38"/>
       <c r="D35" s="38"/>
       <c r="E35" s="45"/>
@@ -3215,7 +3226,7 @@
     </row>
     <row r="36" spans="1:36" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A36" s="44"/>
-      <c r="B36" s="121"/>
+      <c r="B36" s="120"/>
       <c r="C36" s="38"/>
       <c r="D36" s="38"/>
       <c r="E36" s="45"/>
@@ -3236,7 +3247,7 @@
     </row>
     <row r="37" spans="1:36" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A37" s="44"/>
-      <c r="B37" s="121"/>
+      <c r="B37" s="120"/>
       <c r="C37" s="38"/>
       <c r="D37" s="38"/>
       <c r="E37" s="45"/>
@@ -3257,7 +3268,7 @@
     </row>
     <row r="38" spans="1:36" s="35" customFormat="1" ht="18" customHeight="1">
       <c r="A38" s="44"/>
-      <c r="B38" s="121"/>
+      <c r="B38" s="120"/>
       <c r="C38" s="38"/>
       <c r="D38" s="38"/>
       <c r="E38" s="45"/>
@@ -3269,121 +3280,133 @@
       <c r="K38" s="49"/>
       <c r="L38" s="49"/>
       <c r="M38" s="49"/>
-      <c r="N38" s="60"/>
+      <c r="N38" s="49"/>
       <c r="O38" s="49"/>
       <c r="P38" s="49"/>
       <c r="Q38" s="49"/>
       <c r="R38" s="49"/>
       <c r="S38" s="49"/>
-      <c r="T38" s="49"/>
-      <c r="U38" s="49"/>
-      <c r="V38" s="49"/>
-      <c r="W38" s="49"/>
-      <c r="X38" s="49"/>
-      <c r="Y38" s="49"/>
-      <c r="Z38" s="49"/>
-      <c r="AA38" s="49"/>
-      <c r="AB38" s="49"/>
-      <c r="AC38" s="49"/>
-      <c r="AD38" s="49"/>
-      <c r="AE38" s="49"/>
-      <c r="AF38" s="49"/>
-      <c r="AG38" s="49"/>
-      <c r="AH38" s="49"/>
-      <c r="AI38" s="49"/>
-      <c r="AJ38" s="49"/>
-    </row>
-    <row r="39" spans="1:36" s="35" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
-      <c r="A39" s="159">
-        <f>SUM(A23:A32)</f>
+    </row>
+    <row r="39" spans="1:36" s="35" customFormat="1" ht="18" customHeight="1">
+      <c r="A39" s="44"/>
+      <c r="B39" s="120"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="45"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="49"/>
+      <c r="K39" s="49"/>
+      <c r="L39" s="49"/>
+      <c r="M39" s="49"/>
+      <c r="N39" s="60"/>
+      <c r="O39" s="49"/>
+      <c r="P39" s="49"/>
+      <c r="Q39" s="49"/>
+      <c r="R39" s="49"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="49"/>
+      <c r="U39" s="49"/>
+      <c r="V39" s="49"/>
+      <c r="W39" s="49"/>
+      <c r="X39" s="49"/>
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AE39" s="49"/>
+      <c r="AF39" s="49"/>
+      <c r="AG39" s="49"/>
+      <c r="AH39" s="49"/>
+      <c r="AI39" s="49"/>
+      <c r="AJ39" s="49"/>
+    </row>
+    <row r="40" spans="1:36" s="35" customFormat="1" ht="17.45" customHeight="1" thickBot="1">
+      <c r="A40" s="158">
+        <f>SUM(A24:A33)</f>
         <v>390</v>
       </c>
-      <c r="B39" s="185"/>
-      <c r="C39" s="186"/>
-      <c r="D39" s="187"/>
-      <c r="E39" s="92"/>
-      <c r="F39" s="93"/>
-      <c r="G39" s="173">
-        <f>SUM(G23:G32)</f>
+      <c r="B40" s="193"/>
+      <c r="C40" s="194"/>
+      <c r="D40" s="195"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="93"/>
+      <c r="G40" s="172">
+        <f>SUM(G24:G33)</f>
         <v>9110.5</v>
       </c>
-      <c r="H39" s="174">
-        <f>SUM(H23:H32)</f>
+      <c r="H40" s="173">
+        <f>SUM(H24:H33)</f>
         <v>9529</v>
       </c>
-      <c r="I39" s="48"/>
-      <c r="J39" s="140"/>
-      <c r="K39" s="34"/>
-    </row>
-    <row r="40" spans="1:36" s="35" customFormat="1" ht="17.45" customHeight="1" thickTop="1">
-      <c r="A40" s="97"/>
-      <c r="B40" s="98"/>
-      <c r="C40" s="99"/>
-      <c r="D40" s="100"/>
-      <c r="E40" s="101"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="104"/>
       <c r="I40" s="48"/>
-      <c r="J40" s="34"/>
+      <c r="J40" s="139"/>
       <c r="K40" s="34"/>
     </row>
-    <row r="41" spans="1:36" s="35" customFormat="1" ht="16.8" customHeight="1">
-      <c r="A41" s="108"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="59"/>
+    <row r="41" spans="1:36" s="35" customFormat="1" ht="17.45" customHeight="1" thickTop="1">
+      <c r="A41" s="97"/>
+      <c r="B41" s="98"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="100"/>
+      <c r="E41" s="101"/>
+      <c r="F41" s="102"/>
       <c r="G41" s="103"/>
-      <c r="H41" s="109"/>
-      <c r="I41" s="110"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="32"/>
+      <c r="H41" s="104"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
     </row>
     <row r="42" spans="1:36" s="35" customFormat="1" ht="16.8" customHeight="1">
-      <c r="A42" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="A42" s="108"/>
+      <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="181" t="s">
-        <v>0</v>
-      </c>
-      <c r="G42" s="182"/>
-      <c r="H42" s="183"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="109"/>
       <c r="I42" s="110"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="32"/>
     </row>
     <row r="43" spans="1:36" s="35" customFormat="1" ht="16.8" customHeight="1">
-      <c r="A43" s="113"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="1"/>
+      <c r="A43" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="174" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="175"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="111"/>
-      <c r="G43" s="114"/>
-      <c r="H43" s="112"/>
+      <c r="F43" s="190" t="s">
+        <v>0</v>
+      </c>
+      <c r="G43" s="177"/>
+      <c r="H43" s="178"/>
       <c r="I43" s="110"/>
     </row>
-    <row r="44" spans="1:36">
+    <row r="44" spans="1:36" s="35" customFormat="1" ht="16.8" customHeight="1">
       <c r="A44" s="113"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="116"/>
-      <c r="I44" s="117"/>
-    </row>
-    <row r="45" spans="1:36" ht="15.6" customHeight="1">
+      <c r="B44" s="3"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="111"/>
+      <c r="G44" s="114"/>
+      <c r="H44" s="112"/>
+      <c r="I44" s="110"/>
+    </row>
+    <row r="45" spans="1:36">
       <c r="A45" s="113"/>
-      <c r="B45" s="64"/>
-      <c r="E45" s="67"/>
       <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
-      <c r="H45" s="118"/>
+      <c r="G45" s="68"/>
+      <c r="H45" s="116"/>
       <c r="I45" s="117"/>
     </row>
     <row r="46" spans="1:36" ht="15.6" customHeight="1">
@@ -3395,26 +3418,27 @@
       <c r="H46" s="118"/>
       <c r="I46" s="117"/>
     </row>
-    <row r="47" spans="1:36" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A47" s="131"/>
-      <c r="B47" s="127"/>
-      <c r="C47" s="127"/>
-      <c r="D47" s="127"/>
-      <c r="E47" s="132"/>
-      <c r="F47" s="132"/>
-      <c r="G47" s="132"/>
-      <c r="H47" s="133"/>
+    <row r="47" spans="1:36" ht="15.6" customHeight="1">
+      <c r="A47" s="113"/>
+      <c r="B47" s="64"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="118"/>
       <c r="I47" s="117"/>
     </row>
-    <row r="48" spans="1:36" ht="13.8" customHeight="1" thickTop="1">
-      <c r="A48" s="65"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="115"/>
-      <c r="I48" s="115"/>
-    </row>
-    <row r="49" spans="1:9">
+    <row r="48" spans="1:36" ht="13.8" customHeight="1" thickBot="1">
+      <c r="A48" s="130"/>
+      <c r="B48" s="126"/>
+      <c r="C48" s="126"/>
+      <c r="D48" s="126"/>
+      <c r="E48" s="131"/>
+      <c r="F48" s="131"/>
+      <c r="G48" s="131"/>
+      <c r="H48" s="132"/>
+      <c r="I48" s="117"/>
+    </row>
+    <row r="49" spans="1:9" ht="13.8" customHeight="1" thickTop="1">
       <c r="A49" s="65"/>
       <c r="E49" s="65"/>
       <c r="F49" s="65"/>
@@ -3440,18 +3464,26 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="65"/>
+      <c r="E52" s="65"/>
+      <c r="F52" s="65"/>
+      <c r="G52" s="65"/>
+      <c r="H52" s="115"/>
+      <c r="I52" s="115"/>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
